--- a/Hoja de cálculo CHATBOT.xlsx
+++ b/Hoja de cálculo CHATBOT.xlsx
@@ -962,7 +962,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -996,12 +996,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1513,7 +1507,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1537,16 +1531,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1555,85 +1549,85 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1781,7 +1775,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="8" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="7" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1790,13 +1784,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1826,7 +1820,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1838,10 +1832,10 @@
     <xf numFmtId="179" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1853,7 +1847,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1882,7 +1876,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1955,15 +1949,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2004,87 +1998,87 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2858,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="33">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="J20" s="33" t="s">
         <v>11</v>
@@ -2897,7 +2891,7 @@
       </c>
       <c r="I21" s="102">
         <f>I20/D22</f>
-        <v>37.037037037037</v>
+        <v>88.8888888888889</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>17</v>
@@ -2979,7 +2973,7 @@
         <v>32</v>
       </c>
       <c r="I23" s="30">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J23" s="30" t="s">
         <v>33</v>
@@ -3004,7 +2998,7 @@
         <v>36</v>
       </c>
       <c r="D24" s="20">
-        <v>14</v>
+        <v>26.8</v>
       </c>
       <c r="E24" s="22" t="s">
         <v>29</v>
@@ -3205,7 +3199,7 @@
       </c>
       <c r="D31" s="52">
         <f>610.78*EXP((17.269*D24)/(D24+237.3))</f>
-        <v>1598.46346143011</v>
+        <v>3523.24666670556</v>
       </c>
       <c r="E31" s="49" t="s">
         <v>55</v>
@@ -3221,7 +3215,7 @@
       </c>
       <c r="I31" s="108">
         <f>D23-D24</f>
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="J31" s="49" t="s">
         <v>29</v>
@@ -3248,7 +3242,7 @@
       </c>
       <c r="D32" s="55">
         <f>(I23/100)*D31</f>
-        <v>1198.84759607258</v>
+        <v>2431.04020002684</v>
       </c>
       <c r="E32" s="49" t="s">
         <v>55</v>
@@ -3264,7 +3258,7 @@
       </c>
       <c r="I32" s="110">
         <f>(I21*I30*I31*I29)/1000</f>
-        <v>5.38074074074074</v>
+        <v>2.58275555555555</v>
       </c>
       <c r="J32" s="49" t="s">
         <v>71</v>
@@ -3291,7 +3285,7 @@
       </c>
       <c r="D33" s="48">
         <f>(D30-D31)/1000</f>
-        <v>2.64398649115463</v>
+        <v>0.719203285879184</v>
       </c>
       <c r="E33" s="49" t="s">
         <v>75</v>
@@ -3324,7 +3318,7 @@
       </c>
       <c r="D34" s="48">
         <f>(0.089+0.078*0.8)*D33*I21</f>
-        <v>14.8259094355856</v>
+        <v>9.67887799840964</v>
       </c>
       <c r="E34" s="49" t="s">
         <v>80</v>
@@ -3340,7 +3334,7 @@
       </c>
       <c r="I34" s="111">
         <f>(SUM(D43,D35,I32))*0.2</f>
-        <v>4.26300812017994</v>
+        <v>3.70967724989995</v>
       </c>
       <c r="J34" s="49" t="s">
         <v>71</v>
@@ -3366,7 +3360,7 @@
       </c>
       <c r="D35" s="61">
         <f>(D29*D34)/3600</f>
-        <v>9.88393962372374</v>
+        <v>6.45258533227309</v>
       </c>
       <c r="E35" s="62" t="s">
         <v>71</v>
@@ -3438,7 +3432,7 @@
       </c>
       <c r="I37" s="114">
         <f>SUM(D43,D35,I32,I34)</f>
-        <v>25.5780487210796</v>
+        <v>22.2580634993997</v>
       </c>
       <c r="J37" s="115" t="s">
         <v>71</v>
@@ -3456,7 +3450,7 @@
       </c>
       <c r="D38" s="66">
         <f>D24+273</f>
-        <v>287</v>
+        <v>299.8</v>
       </c>
       <c r="E38" s="49" t="s">
         <v>91</v>
@@ -3536,7 +3530,7 @@
       </c>
       <c r="D41" s="73">
         <f>D38^4</f>
-        <v>6784652161</v>
+        <v>8078421590.4016</v>
       </c>
       <c r="E41" s="49" t="s">
         <v>102</v>
@@ -3569,7 +3563,7 @@
       </c>
       <c r="D42" s="73">
         <f>D40-(0.8*D41)</f>
-        <v>3001170752.2</v>
+        <v>1966155208.67872</v>
       </c>
       <c r="E42" s="49" t="s">
         <v>102</v>
@@ -3585,7 +3579,7 @@
       </c>
       <c r="I42" s="77">
         <f>D23-(D24-2)</f>
-        <v>18</v>
+        <v>5.2</v>
       </c>
       <c r="J42" s="119" t="s">
         <v>29</v>
@@ -3603,7 +3597,7 @@
       </c>
       <c r="D43" s="66">
         <f>(I21*D39*0.96*D42)/1000</f>
-        <v>6.0503602364352</v>
+        <v>9.51304536167111</v>
       </c>
       <c r="E43" s="75" t="s">
         <v>71</v>
@@ -3619,7 +3613,7 @@
       </c>
       <c r="I43" s="110">
         <f>I20*I42*I41*I40/3600</f>
-        <v>1042.91</v>
+        <v>723.084266666667</v>
       </c>
       <c r="J43" s="75" t="s">
         <v>120</v>
@@ -4149,7 +4143,7 @@
       </c>
       <c r="I69" s="158">
         <f>I43</f>
-        <v>1042.91</v>
+        <v>723.084266666667</v>
       </c>
       <c r="J69" s="119" t="s">
         <v>120</v>
@@ -4167,7 +4161,7 @@
       </c>
       <c r="D70" s="128">
         <f>D24</f>
-        <v>14</v>
+        <v>26.8</v>
       </c>
       <c r="E70" s="128" t="s">
         <v>29</v>
@@ -4183,7 +4177,7 @@
       </c>
       <c r="I70" s="159">
         <f>D68-I37</f>
-        <v>1.42195127892038</v>
+        <v>4.74193650060029</v>
       </c>
       <c r="J70" s="119" t="s">
         <v>71</v>
@@ -4212,7 +4206,7 @@
       </c>
       <c r="I71" s="77">
         <f>I69/(I70*I68)</f>
-        <v>73.3435818414139</v>
+        <v>15.2487125581528</v>
       </c>
       <c r="J71" s="119" t="s">
         <v>174</v>
@@ -4270,7 +4264,7 @@
       </c>
       <c r="D74" s="137">
         <f>I37/D71</f>
-        <v>4.26300812017994</v>
+        <v>3.70967724989995</v>
       </c>
       <c r="E74" s="138" t="s">
         <v>71</v>
@@ -4301,7 +4295,7 @@
       </c>
       <c r="D75" s="137">
         <f>D74*24</f>
-        <v>102.312194884319</v>
+        <v>89.0322539975988</v>
       </c>
       <c r="E75" s="138" t="s">
         <v>202</v>
@@ -4332,7 +4326,7 @@
       </c>
       <c r="D76" s="137">
         <f>D75*30*0.7</f>
-        <v>2148.55609257069</v>
+        <v>1869.67733394958</v>
       </c>
       <c r="E76" s="138" t="s">
         <v>207</v>
@@ -4393,7 +4387,7 @@
       </c>
       <c r="D78" s="141">
         <f>D76*D77</f>
-        <v>1503989.26479948</v>
+        <v>1308774.1337647</v>
       </c>
       <c r="E78" s="142"/>
       <c r="F78" s="54" t="s">
@@ -4657,7 +4651,7 @@
       </c>
       <c r="I88" s="160">
         <f>I20</f>
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="J88" s="161" t="s">
         <v>11</v>
@@ -5021,7 +5015,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E92 E94" evalError="1"/>
+    <ignoredError sqref="E94 E92" evalError="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5053,7 +5047,7 @@
       </c>
       <c r="C4" s="1">
         <f>'Hoja de cálculo V1'!I37</f>
-        <v>25.5780487210796</v>
+        <v>22.2580634993997</v>
       </c>
     </row>
     <row r="7" spans="2:8">
